--- a/artfynd/A 56894-2022 artfynd.xlsx
+++ b/artfynd/A 56894-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56894-2022 artfynd.xlsx
+++ b/artfynd/A 56894-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2443,6 +2443,5126 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120498307</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>512792</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7128772</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120500539</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78187</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>353</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>512939</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7128343</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120499316</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>512920</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7128544</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120497952</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>512703</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7128859</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120498176</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>512770</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7128772</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120500096</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>512986</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7128475</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120500243</v>
+      </c>
+      <c r="B23" t="n">
+        <v>90576</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>513023</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7128467</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120498715</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80499</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>512849</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7128712</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120495559</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78187</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>353</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>512948</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7128805</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120495447</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79527</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>513004</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7128839</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120498006</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>512721</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7128827</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120499221</v>
+      </c>
+      <c r="B28" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>512894</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7128619</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120499507</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>512911</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7128542</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120498401</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>512865</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7128745</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120501523</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79583</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>513173</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7128614</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120499737</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>512923</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7128512</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120495063</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>513054</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7128890</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120495236</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>513040</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7128866</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120499625</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>512933</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7128535</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120501177</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>513078</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7128470</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120500528</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78278</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>512943</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7128349</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120495327</v>
+      </c>
+      <c r="B38" t="n">
+        <v>90576</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>513039</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7128873</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120494284</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>513104</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7128997</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>120494800</v>
+      </c>
+      <c r="B40" t="n">
+        <v>78187</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>353</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>513056</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7128924</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>120499482</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79659</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>512911</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7128542</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>120495537</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79131</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>512947</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7128818</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>120498596</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79652</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>512850</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7128717</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>120498027</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79659</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>512716</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7128822</v>
+      </c>
+      <c r="S44" t="n">
+        <v>15</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>120499409</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79131</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>512923</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7128543</v>
+      </c>
+      <c r="S45" t="n">
+        <v>15</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>120494756</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>513061</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7128929</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på granlåga</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>120501722</v>
+      </c>
+      <c r="B47" t="n">
+        <v>78187</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>353</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>513207</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7128708</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>120494019</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>513140</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7129010</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>120499055</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>512881</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7128617</v>
+      </c>
+      <c r="S49" t="n">
+        <v>15</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>120498585</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>512853</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7128713</v>
+      </c>
+      <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>120497877</v>
+      </c>
+      <c r="B51" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>512692</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7128875</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>120499332</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79659</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>512919</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7128556</v>
+      </c>
+      <c r="S52" t="n">
+        <v>15</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>120499521</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>512916</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7128556</v>
+      </c>
+      <c r="S53" t="n">
+        <v>15</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>120498729</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79131</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>512852</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7128719</v>
+      </c>
+      <c r="S54" t="n">
+        <v>15</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>120498577</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>512845</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7128718</v>
+      </c>
+      <c r="S55" t="n">
+        <v>15</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>120500304</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>513030</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7128399</v>
+      </c>
+      <c r="S56" t="n">
+        <v>15</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>120501050</v>
+      </c>
+      <c r="B57" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>513045</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7128377</v>
+      </c>
+      <c r="S57" t="n">
+        <v>15</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>120494243</v>
+      </c>
+      <c r="B58" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>513112</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7129001</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>120498915</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>512876</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7128686</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>120500180</v>
+      </c>
+      <c r="B60" t="n">
+        <v>90864</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>658</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>512964</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7128462</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>120498172</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>512757</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7128774</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>120499446</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79658</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>512906</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7128551</v>
+      </c>
+      <c r="S62" t="n">
+        <v>15</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>120493980</v>
+      </c>
+      <c r="B63" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>513141</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7129006</v>
+      </c>
+      <c r="S63" t="n">
+        <v>15</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>120494059</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79658</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>513140</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7129002</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>120498298</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>512796</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7128766</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>120498239</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>512784</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7128764</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56894-2022 artfynd.xlsx
+++ b/artfynd/A 56894-2022 artfynd.xlsx
@@ -2649,7 +2649,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120499316</v>
+        <v>120497952</v>
       </c>
       <c r="B19" t="n">
         <v>79624</v>
@@ -2685,17 +2685,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>512920</v>
+        <v>512703</v>
       </c>
       <c r="R19" t="n">
-        <v>7128544</v>
+        <v>7128859</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120497952</v>
+        <v>120499316</v>
       </c>
       <c r="B20" t="n">
         <v>79624</v>
@@ -2787,17 +2787,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>512703</v>
+        <v>512920</v>
       </c>
       <c r="R20" t="n">
-        <v>7128859</v>
+        <v>7128544</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120499507</v>
+        <v>120499737</v>
       </c>
       <c r="B29" t="n">
         <v>79623</v>
@@ -3719,13 +3719,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>512911</v>
+        <v>512923</v>
       </c>
       <c r="R29" t="n">
-        <v>7128542</v>
+        <v>7128512</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3781,10 +3781,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120498401</v>
+        <v>120501523</v>
       </c>
       <c r="B30" t="n">
-        <v>79624</v>
+        <v>79583</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3793,38 +3793,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>229497</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>512865</v>
+        <v>513173</v>
       </c>
       <c r="R30" t="n">
-        <v>7128745</v>
+        <v>7128614</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3883,10 +3883,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120501523</v>
+        <v>120498401</v>
       </c>
       <c r="B31" t="n">
-        <v>79583</v>
+        <v>79624</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3895,38 +3895,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229497</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>513173</v>
+        <v>512865</v>
       </c>
       <c r="R31" t="n">
-        <v>7128614</v>
+        <v>7128745</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3985,7 +3985,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120499737</v>
+        <v>120499507</v>
       </c>
       <c r="B32" t="n">
         <v>79623</v>
@@ -4025,13 +4025,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>512923</v>
+        <v>512911</v>
       </c>
       <c r="R32" t="n">
-        <v>7128512</v>
+        <v>7128542</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4597,10 +4597,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120495327</v>
+        <v>120494284</v>
       </c>
       <c r="B38" t="n">
-        <v>90576</v>
+        <v>79624</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4613,21 +4613,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>513039</v>
+        <v>513104</v>
       </c>
       <c r="R38" t="n">
-        <v>7128873</v>
+        <v>7128997</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4699,10 +4699,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120494284</v>
+        <v>120494800</v>
       </c>
       <c r="B39" t="n">
-        <v>79624</v>
+        <v>78187</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4715,21 +4715,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4739,10 +4739,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>513104</v>
+        <v>513056</v>
       </c>
       <c r="R39" t="n">
-        <v>7128997</v>
+        <v>7128924</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4801,10 +4801,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120494800</v>
+        <v>120499482</v>
       </c>
       <c r="B40" t="n">
-        <v>78187</v>
+        <v>79659</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4813,38 +4813,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>513056</v>
+        <v>512911</v>
       </c>
       <c r="R40" t="n">
-        <v>7128924</v>
+        <v>7128542</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4903,10 +4903,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120499482</v>
+        <v>120495327</v>
       </c>
       <c r="B41" t="n">
-        <v>79659</v>
+        <v>90576</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4915,41 +4915,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>512911</v>
+        <v>513039</v>
       </c>
       <c r="R41" t="n">
-        <v>7128542</v>
+        <v>7128873</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5005,10 +5005,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120495537</v>
+        <v>120498027</v>
       </c>
       <c r="B42" t="n">
-        <v>79131</v>
+        <v>79659</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5017,25 +5017,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>6464</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>512947</v>
+        <v>512716</v>
       </c>
       <c r="R42" t="n">
-        <v>7128818</v>
+        <v>7128822</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5107,10 +5107,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120498596</v>
+        <v>120495537</v>
       </c>
       <c r="B43" t="n">
-        <v>79652</v>
+        <v>79131</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5119,25 +5119,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5147,10 +5147,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>512850</v>
+        <v>512947</v>
       </c>
       <c r="R43" t="n">
-        <v>7128717</v>
+        <v>7128818</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5209,10 +5209,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120498027</v>
+        <v>120499409</v>
       </c>
       <c r="B44" t="n">
-        <v>79659</v>
+        <v>79131</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5221,38 +5221,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>512716</v>
+        <v>512923</v>
       </c>
       <c r="R44" t="n">
-        <v>7128822</v>
+        <v>7128543</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5311,10 +5311,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120499409</v>
+        <v>120498596</v>
       </c>
       <c r="B45" t="n">
-        <v>79131</v>
+        <v>79652</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5323,38 +5323,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>512923</v>
+        <v>512850</v>
       </c>
       <c r="R45" t="n">
-        <v>7128543</v>
+        <v>7128717</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5627,7 +5627,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120494019</v>
+        <v>120499055</v>
       </c>
       <c r="B48" t="n">
         <v>79624</v>
@@ -5667,10 +5667,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>513140</v>
+        <v>512881</v>
       </c>
       <c r="R48" t="n">
-        <v>7129010</v>
+        <v>7128617</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5729,10 +5729,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120499055</v>
+        <v>120498585</v>
       </c>
       <c r="B49" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5745,21 +5745,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>512881</v>
+        <v>512853</v>
       </c>
       <c r="R49" t="n">
-        <v>7128617</v>
+        <v>7128713</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5831,10 +5831,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120498585</v>
+        <v>120494019</v>
       </c>
       <c r="B50" t="n">
-        <v>79623</v>
+        <v>79624</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5847,21 +5847,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5871,10 +5871,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>512853</v>
+        <v>513140</v>
       </c>
       <c r="R50" t="n">
-        <v>7128713</v>
+        <v>7129010</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6647,10 +6647,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120494243</v>
+        <v>120500180</v>
       </c>
       <c r="B58" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6663,34 +6663,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>513112</v>
+        <v>512964</v>
       </c>
       <c r="R58" t="n">
-        <v>7129001</v>
+        <v>7128462</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6749,10 +6749,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120498915</v>
+        <v>120494243</v>
       </c>
       <c r="B59" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6765,21 +6765,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6789,10 +6789,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>512876</v>
+        <v>513112</v>
       </c>
       <c r="R59" t="n">
-        <v>7128686</v>
+        <v>7129001</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6851,10 +6851,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120500180</v>
+        <v>120498915</v>
       </c>
       <c r="B60" t="n">
-        <v>90864</v>
+        <v>79623</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6867,34 +6867,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>512964</v>
+        <v>512876</v>
       </c>
       <c r="R60" t="n">
-        <v>7128462</v>
+        <v>7128686</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7157,10 +7157,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120493980</v>
+        <v>120498298</v>
       </c>
       <c r="B63" t="n">
-        <v>91858</v>
+        <v>79624</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7169,25 +7169,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7197,13 +7197,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>513141</v>
+        <v>512796</v>
       </c>
       <c r="R63" t="n">
-        <v>7129006</v>
+        <v>7128766</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7259,10 +7259,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120494059</v>
+        <v>120498239</v>
       </c>
       <c r="B64" t="n">
-        <v>79658</v>
+        <v>79623</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7271,25 +7271,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7299,10 +7299,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>513140</v>
+        <v>512784</v>
       </c>
       <c r="R64" t="n">
-        <v>7129002</v>
+        <v>7128764</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7361,10 +7361,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120498298</v>
+        <v>120493980</v>
       </c>
       <c r="B65" t="n">
-        <v>79624</v>
+        <v>91858</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7373,25 +7373,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7401,13 +7401,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>512796</v>
+        <v>513141</v>
       </c>
       <c r="R65" t="n">
-        <v>7128766</v>
+        <v>7129006</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7463,10 +7463,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120498239</v>
+        <v>120494059</v>
       </c>
       <c r="B66" t="n">
-        <v>79623</v>
+        <v>79658</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7475,25 +7475,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7503,10 +7503,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>512784</v>
+        <v>513140</v>
       </c>
       <c r="R66" t="n">
-        <v>7128764</v>
+        <v>7129002</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>

--- a/artfynd/A 56894-2022 artfynd.xlsx
+++ b/artfynd/A 56894-2022 artfynd.xlsx
@@ -2445,10 +2445,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120498307</v>
+        <v>120499446</v>
       </c>
       <c r="B17" t="n">
-        <v>79623</v>
+        <v>79658</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2457,38 +2457,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>512792</v>
+        <v>512906</v>
       </c>
       <c r="R17" t="n">
-        <v>7128772</v>
+        <v>7128551</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2547,7 +2547,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120500539</v>
+        <v>120495559</v>
       </c>
       <c r="B18" t="n">
         <v>78187</v>
@@ -2583,17 +2583,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>512939</v>
+        <v>512948</v>
       </c>
       <c r="R18" t="n">
-        <v>7128343</v>
+        <v>7128805</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120497952</v>
+        <v>120498298</v>
       </c>
       <c r="B19" t="n">
         <v>79624</v>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>512703</v>
+        <v>512796</v>
       </c>
       <c r="R19" t="n">
-        <v>7128859</v>
+        <v>7128766</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2751,10 +2751,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120499316</v>
+        <v>120501722</v>
       </c>
       <c r="B20" t="n">
-        <v>79624</v>
+        <v>78187</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2767,21 +2767,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2791,13 +2791,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>512920</v>
+        <v>513207</v>
       </c>
       <c r="R20" t="n">
-        <v>7128544</v>
+        <v>7128708</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120498176</v>
+        <v>120500304</v>
       </c>
       <c r="B21" t="n">
         <v>79624</v>
@@ -2889,14 +2889,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>512770</v>
+        <v>513030</v>
       </c>
       <c r="R21" t="n">
-        <v>7128772</v>
+        <v>7128399</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2955,10 +2955,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120500096</v>
+        <v>120500243</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2971,42 +2971,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>512986</v>
+        <v>513023</v>
       </c>
       <c r="R22" t="n">
-        <v>7128475</v>
+        <v>7128467</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3036,11 +3031,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3067,10 +3057,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120500243</v>
+        <v>120494800</v>
       </c>
       <c r="B23" t="n">
-        <v>90576</v>
+        <v>78187</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3083,37 +3073,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>513023</v>
+        <v>513056</v>
       </c>
       <c r="R23" t="n">
-        <v>7128467</v>
+        <v>7128924</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3169,10 +3159,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120498715</v>
+        <v>120499409</v>
       </c>
       <c r="B24" t="n">
-        <v>80499</v>
+        <v>79131</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3185,34 +3175,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1049</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>512849</v>
+        <v>512923</v>
       </c>
       <c r="R24" t="n">
-        <v>7128712</v>
+        <v>7128543</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3271,10 +3261,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120495559</v>
+        <v>120494019</v>
       </c>
       <c r="B25" t="n">
-        <v>78187</v>
+        <v>79624</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3287,21 +3277,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3311,13 +3301,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>512948</v>
+        <v>513140</v>
       </c>
       <c r="R25" t="n">
-        <v>7128805</v>
+        <v>7129010</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3373,10 +3363,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120495447</v>
+        <v>120499521</v>
       </c>
       <c r="B26" t="n">
-        <v>79527</v>
+        <v>79624</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3385,41 +3375,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>513004</v>
+        <v>512916</v>
       </c>
       <c r="R26" t="n">
-        <v>7128839</v>
+        <v>7128556</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3577,10 +3567,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120499221</v>
+        <v>120500528</v>
       </c>
       <c r="B28" t="n">
-        <v>90580</v>
+        <v>78278</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3593,34 +3583,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>512894</v>
+        <v>512943</v>
       </c>
       <c r="R28" t="n">
-        <v>7128619</v>
+        <v>7128349</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3679,10 +3669,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120499737</v>
+        <v>120495063</v>
       </c>
       <c r="B29" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3695,37 +3685,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>512923</v>
+        <v>513054</v>
       </c>
       <c r="R29" t="n">
-        <v>7128512</v>
+        <v>7128890</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3781,10 +3771,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120501523</v>
+        <v>120497877</v>
       </c>
       <c r="B30" t="n">
-        <v>79583</v>
+        <v>78542</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3793,38 +3783,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>513173</v>
+        <v>512692</v>
       </c>
       <c r="R30" t="n">
-        <v>7128614</v>
+        <v>7128875</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3883,10 +3873,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120498401</v>
+        <v>120494243</v>
       </c>
       <c r="B31" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3899,21 +3889,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3923,10 +3913,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>512865</v>
+        <v>513112</v>
       </c>
       <c r="R31" t="n">
-        <v>7128745</v>
+        <v>7129001</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3985,7 +3975,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120499507</v>
+        <v>120498172</v>
       </c>
       <c r="B32" t="n">
         <v>79623</v>
@@ -4021,17 +4011,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>512911</v>
+        <v>512757</v>
       </c>
       <c r="R32" t="n">
-        <v>7128542</v>
+        <v>7128774</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4087,10 +4077,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120495063</v>
+        <v>120499482</v>
       </c>
       <c r="B33" t="n">
-        <v>78542</v>
+        <v>79659</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4099,38 +4089,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>513054</v>
+        <v>512911</v>
       </c>
       <c r="R33" t="n">
-        <v>7128890</v>
+        <v>7128542</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4189,10 +4179,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120495236</v>
+        <v>120499625</v>
       </c>
       <c r="B34" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4205,34 +4195,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>513040</v>
+        <v>512933</v>
       </c>
       <c r="R34" t="n">
-        <v>7128866</v>
+        <v>7128535</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4291,10 +4281,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120499625</v>
+        <v>120498577</v>
       </c>
       <c r="B35" t="n">
-        <v>79623</v>
+        <v>79624</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4307,37 +4297,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>512933</v>
+        <v>512845</v>
       </c>
       <c r="R35" t="n">
-        <v>7128535</v>
+        <v>7128718</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4393,10 +4383,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120501177</v>
+        <v>120500180</v>
       </c>
       <c r="B36" t="n">
-        <v>79624</v>
+        <v>90864</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4409,21 +4399,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4433,10 +4423,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>513078</v>
+        <v>512964</v>
       </c>
       <c r="R36" t="n">
-        <v>7128470</v>
+        <v>7128462</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4495,10 +4485,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120500528</v>
+        <v>120499221</v>
       </c>
       <c r="B37" t="n">
-        <v>78278</v>
+        <v>90580</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4511,34 +4501,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>512943</v>
+        <v>512894</v>
       </c>
       <c r="R37" t="n">
-        <v>7128349</v>
+        <v>7128619</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4597,10 +4587,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120494284</v>
+        <v>120494059</v>
       </c>
       <c r="B38" t="n">
-        <v>79624</v>
+        <v>79658</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4609,25 +4599,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4637,13 +4627,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>513104</v>
+        <v>513140</v>
       </c>
       <c r="R38" t="n">
-        <v>7128997</v>
+        <v>7129002</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4699,10 +4689,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120494800</v>
+        <v>120499332</v>
       </c>
       <c r="B39" t="n">
-        <v>78187</v>
+        <v>79659</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4711,38 +4701,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>513056</v>
+        <v>512919</v>
       </c>
       <c r="R39" t="n">
-        <v>7128924</v>
+        <v>7128556</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4801,10 +4791,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120499482</v>
+        <v>120495447</v>
       </c>
       <c r="B40" t="n">
-        <v>79659</v>
+        <v>79527</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4817,37 +4807,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>6456</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>512911</v>
+        <v>513004</v>
       </c>
       <c r="R40" t="n">
-        <v>7128542</v>
+        <v>7128839</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4903,10 +4893,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120495327</v>
+        <v>120498239</v>
       </c>
       <c r="B41" t="n">
-        <v>90576</v>
+        <v>79623</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4919,21 +4909,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4943,10 +4933,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>513039</v>
+        <v>512784</v>
       </c>
       <c r="R41" t="n">
-        <v>7128873</v>
+        <v>7128764</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5005,10 +4995,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120498027</v>
+        <v>120498176</v>
       </c>
       <c r="B42" t="n">
-        <v>79659</v>
+        <v>79624</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5017,25 +5007,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5045,10 +5035,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>512716</v>
+        <v>512770</v>
       </c>
       <c r="R42" t="n">
-        <v>7128822</v>
+        <v>7128772</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5107,10 +5097,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120495537</v>
+        <v>120499316</v>
       </c>
       <c r="B43" t="n">
-        <v>79131</v>
+        <v>79624</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5123,34 +5113,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>512947</v>
+        <v>512920</v>
       </c>
       <c r="R43" t="n">
-        <v>7128818</v>
+        <v>7128544</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5209,10 +5199,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120499409</v>
+        <v>120498596</v>
       </c>
       <c r="B44" t="n">
-        <v>79131</v>
+        <v>79652</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5221,38 +5211,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>512923</v>
+        <v>512850</v>
       </c>
       <c r="R44" t="n">
-        <v>7128543</v>
+        <v>7128717</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5311,10 +5301,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120498596</v>
+        <v>120498307</v>
       </c>
       <c r="B45" t="n">
-        <v>79652</v>
+        <v>79623</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5323,25 +5313,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5351,10 +5341,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>512850</v>
+        <v>512792</v>
       </c>
       <c r="R45" t="n">
-        <v>7128717</v>
+        <v>7128772</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5413,10 +5403,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120494756</v>
+        <v>120501523</v>
       </c>
       <c r="B46" t="n">
-        <v>57320</v>
+        <v>79583</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5425,43 +5415,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>513061</v>
+        <v>513173</v>
       </c>
       <c r="R46" t="n">
-        <v>7128929</v>
+        <v>7128614</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5494,11 +5479,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på granlåga</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5525,10 +5505,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120501722</v>
+        <v>120499507</v>
       </c>
       <c r="B47" t="n">
-        <v>78187</v>
+        <v>79623</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5541,21 +5521,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5565,13 +5545,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>513207</v>
+        <v>512911</v>
       </c>
       <c r="R47" t="n">
-        <v>7128708</v>
+        <v>7128542</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5627,10 +5607,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120499055</v>
+        <v>120495236</v>
       </c>
       <c r="B48" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5643,21 +5623,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5667,13 +5647,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>512881</v>
+        <v>513040</v>
       </c>
       <c r="R48" t="n">
-        <v>7128617</v>
+        <v>7128866</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5729,10 +5709,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120498585</v>
+        <v>120495327</v>
       </c>
       <c r="B49" t="n">
-        <v>79623</v>
+        <v>90576</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5745,21 +5725,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5769,13 +5749,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>512853</v>
+        <v>513039</v>
       </c>
       <c r="R49" t="n">
-        <v>7128713</v>
+        <v>7128873</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5831,10 +5811,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120494019</v>
+        <v>120501050</v>
       </c>
       <c r="B50" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5847,34 +5827,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>513140</v>
+        <v>513045</v>
       </c>
       <c r="R50" t="n">
-        <v>7129010</v>
+        <v>7128377</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5933,10 +5913,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120497877</v>
+        <v>120498715</v>
       </c>
       <c r="B51" t="n">
-        <v>78542</v>
+        <v>80499</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5949,21 +5929,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5973,13 +5953,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>512692</v>
+        <v>512849</v>
       </c>
       <c r="R51" t="n">
-        <v>7128875</v>
+        <v>7128712</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6035,7 +6015,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120499332</v>
+        <v>120498027</v>
       </c>
       <c r="B52" t="n">
         <v>79659</v>
@@ -6071,14 +6051,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>512919</v>
+        <v>512716</v>
       </c>
       <c r="R52" t="n">
-        <v>7128556</v>
+        <v>7128822</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6137,7 +6117,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120499521</v>
+        <v>120497952</v>
       </c>
       <c r="B53" t="n">
         <v>79624</v>
@@ -6173,17 +6153,17 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>512916</v>
+        <v>512703</v>
       </c>
       <c r="R53" t="n">
-        <v>7128556</v>
+        <v>7128859</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6239,10 +6219,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120498729</v>
+        <v>120494756</v>
       </c>
       <c r="B54" t="n">
-        <v>79131</v>
+        <v>57320</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6255,37 +6235,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>512852</v>
+        <v>513061</v>
       </c>
       <c r="R54" t="n">
-        <v>7128719</v>
+        <v>7128929</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6315,6 +6300,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på granlåga</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6341,10 +6331,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120498577</v>
+        <v>120498729</v>
       </c>
       <c r="B55" t="n">
-        <v>79624</v>
+        <v>79131</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6357,21 +6347,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6381,10 +6371,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>512845</v>
+        <v>512852</v>
       </c>
       <c r="R55" t="n">
-        <v>7128718</v>
+        <v>7128719</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6443,10 +6433,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120500304</v>
+        <v>120495537</v>
       </c>
       <c r="B56" t="n">
-        <v>79624</v>
+        <v>79131</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6459,34 +6449,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>513030</v>
+        <v>512947</v>
       </c>
       <c r="R56" t="n">
-        <v>7128399</v>
+        <v>7128818</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6545,10 +6535,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120501050</v>
+        <v>120500096</v>
       </c>
       <c r="B57" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6561,34 +6551,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>513045</v>
+        <v>512986</v>
       </c>
       <c r="R57" t="n">
-        <v>7128377</v>
+        <v>7128475</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6621,6 +6616,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6647,10 +6647,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120500180</v>
+        <v>120494284</v>
       </c>
       <c r="B58" t="n">
-        <v>90864</v>
+        <v>79624</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6663,37 +6663,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>512964</v>
+        <v>513104</v>
       </c>
       <c r="R58" t="n">
-        <v>7128462</v>
+        <v>7128997</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6749,10 +6749,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120494243</v>
+        <v>120498585</v>
       </c>
       <c r="B59" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6765,21 +6765,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6789,13 +6789,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>513112</v>
+        <v>512853</v>
       </c>
       <c r="R59" t="n">
-        <v>7129001</v>
+        <v>7128713</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6953,10 +6953,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120498172</v>
+        <v>120493980</v>
       </c>
       <c r="B61" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6965,25 +6965,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6993,13 +6993,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>512757</v>
+        <v>513141</v>
       </c>
       <c r="R61" t="n">
-        <v>7128774</v>
+        <v>7129006</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7055,10 +7055,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120499446</v>
+        <v>120498401</v>
       </c>
       <c r="B62" t="n">
-        <v>79658</v>
+        <v>79624</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7067,41 +7067,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>512906</v>
+        <v>512865</v>
       </c>
       <c r="R62" t="n">
-        <v>7128551</v>
+        <v>7128745</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7157,10 +7157,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120498298</v>
+        <v>120500539</v>
       </c>
       <c r="B63" t="n">
-        <v>79624</v>
+        <v>78187</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7173,37 +7173,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>512796</v>
+        <v>512939</v>
       </c>
       <c r="R63" t="n">
-        <v>7128766</v>
+        <v>7128343</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120498239</v>
+        <v>120499737</v>
       </c>
       <c r="B64" t="n">
         <v>79623</v>
@@ -7295,14 +7295,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>512784</v>
+        <v>512923</v>
       </c>
       <c r="R64" t="n">
-        <v>7128764</v>
+        <v>7128512</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7361,10 +7361,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120493980</v>
+        <v>120499055</v>
       </c>
       <c r="B65" t="n">
-        <v>91858</v>
+        <v>79624</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7373,25 +7373,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7401,10 +7401,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>513141</v>
+        <v>512881</v>
       </c>
       <c r="R65" t="n">
-        <v>7129006</v>
+        <v>7128617</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7463,10 +7463,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120494059</v>
+        <v>120501177</v>
       </c>
       <c r="B66" t="n">
-        <v>79658</v>
+        <v>79624</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7475,38 +7475,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>513140</v>
+        <v>513078</v>
       </c>
       <c r="R66" t="n">
-        <v>7129002</v>
+        <v>7128470</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>

--- a/artfynd/A 56894-2022 artfynd.xlsx
+++ b/artfynd/A 56894-2022 artfynd.xlsx
@@ -2445,10 +2445,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120499446</v>
+        <v>120501177</v>
       </c>
       <c r="B17" t="n">
-        <v>79658</v>
+        <v>79624</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2457,25 +2457,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2485,13 +2485,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>512906</v>
+        <v>513078</v>
       </c>
       <c r="R17" t="n">
-        <v>7128551</v>
+        <v>7128470</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2547,10 +2547,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120495559</v>
+        <v>120494059</v>
       </c>
       <c r="B18" t="n">
-        <v>78187</v>
+        <v>79658</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2559,25 +2559,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>512948</v>
+        <v>513140</v>
       </c>
       <c r="R18" t="n">
-        <v>7128805</v>
+        <v>7129002</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2649,10 +2649,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120498298</v>
+        <v>120495327</v>
       </c>
       <c r="B19" t="n">
-        <v>79624</v>
+        <v>90576</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2665,21 +2665,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>512796</v>
+        <v>513039</v>
       </c>
       <c r="R19" t="n">
-        <v>7128766</v>
+        <v>7128873</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2751,10 +2751,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120501722</v>
+        <v>120493980</v>
       </c>
       <c r="B20" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2763,41 +2763,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>513207</v>
+        <v>513141</v>
       </c>
       <c r="R20" t="n">
-        <v>7128708</v>
+        <v>7129006</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2853,10 +2853,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120500304</v>
+        <v>120498006</v>
       </c>
       <c r="B21" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2869,37 +2869,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>513030</v>
+        <v>512721</v>
       </c>
       <c r="R21" t="n">
-        <v>7128399</v>
+        <v>7128827</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2955,10 +2955,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120500243</v>
+        <v>120498176</v>
       </c>
       <c r="B22" t="n">
-        <v>90576</v>
+        <v>79624</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>513023</v>
+        <v>512770</v>
       </c>
       <c r="R22" t="n">
-        <v>7128467</v>
+        <v>7128772</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3057,10 +3057,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120494800</v>
+        <v>120498915</v>
       </c>
       <c r="B23" t="n">
-        <v>78187</v>
+        <v>79623</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3073,21 +3073,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3097,13 +3097,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>513056</v>
+        <v>512876</v>
       </c>
       <c r="R23" t="n">
-        <v>7128924</v>
+        <v>7128686</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120499409</v>
+        <v>120495537</v>
       </c>
       <c r="B24" t="n">
         <v>79131</v>
@@ -3195,14 +3195,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>512923</v>
+        <v>512947</v>
       </c>
       <c r="R24" t="n">
-        <v>7128543</v>
+        <v>7128818</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3261,10 +3261,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120494019</v>
+        <v>120497877</v>
       </c>
       <c r="B25" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3277,21 +3277,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3301,13 +3301,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>513140</v>
+        <v>512692</v>
       </c>
       <c r="R25" t="n">
-        <v>7129010</v>
+        <v>7128875</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3363,10 +3363,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120499521</v>
+        <v>120498585</v>
       </c>
       <c r="B26" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3379,34 +3379,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>512916</v>
+        <v>512853</v>
       </c>
       <c r="R26" t="n">
-        <v>7128556</v>
+        <v>7128713</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3465,7 +3465,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120498006</v>
+        <v>120499507</v>
       </c>
       <c r="B27" t="n">
         <v>79623</v>
@@ -3501,17 +3501,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>512721</v>
+        <v>512911</v>
       </c>
       <c r="R27" t="n">
-        <v>7128827</v>
+        <v>7128542</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3567,10 +3567,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120500528</v>
+        <v>120498715</v>
       </c>
       <c r="B28" t="n">
-        <v>78278</v>
+        <v>80499</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3583,34 +3583,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>512943</v>
+        <v>512849</v>
       </c>
       <c r="R28" t="n">
-        <v>7128349</v>
+        <v>7128712</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3669,10 +3669,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120495063</v>
+        <v>120499625</v>
       </c>
       <c r="B29" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3685,37 +3685,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>513054</v>
+        <v>512933</v>
       </c>
       <c r="R29" t="n">
-        <v>7128890</v>
+        <v>7128535</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3771,10 +3771,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120497877</v>
+        <v>120498596</v>
       </c>
       <c r="B30" t="n">
-        <v>78542</v>
+        <v>79652</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3783,25 +3783,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3811,13 +3811,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>512692</v>
+        <v>512850</v>
       </c>
       <c r="R30" t="n">
-        <v>7128875</v>
+        <v>7128717</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120494243</v>
+        <v>120495063</v>
       </c>
       <c r="B31" t="n">
         <v>78542</v>
@@ -3913,13 +3913,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>513112</v>
+        <v>513054</v>
       </c>
       <c r="R31" t="n">
-        <v>7129001</v>
+        <v>7128890</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120498172</v>
+        <v>120499737</v>
       </c>
       <c r="B32" t="n">
         <v>79623</v>
@@ -4011,14 +4011,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>512757</v>
+        <v>512923</v>
       </c>
       <c r="R32" t="n">
-        <v>7128774</v>
+        <v>7128512</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4077,10 +4077,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120499482</v>
+        <v>120500539</v>
       </c>
       <c r="B33" t="n">
-        <v>79659</v>
+        <v>78187</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4089,25 +4089,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6464</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4117,10 +4117,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>512911</v>
+        <v>512939</v>
       </c>
       <c r="R33" t="n">
-        <v>7128542</v>
+        <v>7128343</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4179,10 +4179,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120499625</v>
+        <v>120500528</v>
       </c>
       <c r="B34" t="n">
-        <v>79623</v>
+        <v>78278</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4195,21 +4195,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4219,13 +4219,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>512933</v>
+        <v>512943</v>
       </c>
       <c r="R34" t="n">
-        <v>7128535</v>
+        <v>7128349</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4281,10 +4281,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120498577</v>
+        <v>120495559</v>
       </c>
       <c r="B35" t="n">
-        <v>79624</v>
+        <v>78187</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4297,21 +4297,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4321,13 +4321,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>512845</v>
+        <v>512948</v>
       </c>
       <c r="R35" t="n">
-        <v>7128718</v>
+        <v>7128805</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4383,10 +4383,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120500180</v>
+        <v>120498172</v>
       </c>
       <c r="B36" t="n">
-        <v>90864</v>
+        <v>79623</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4399,34 +4399,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>512964</v>
+        <v>512757</v>
       </c>
       <c r="R36" t="n">
-        <v>7128462</v>
+        <v>7128774</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4485,10 +4485,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120499221</v>
+        <v>120494243</v>
       </c>
       <c r="B37" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4501,21 +4501,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4525,13 +4525,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>512894</v>
+        <v>513112</v>
       </c>
       <c r="R37" t="n">
-        <v>7128619</v>
+        <v>7129001</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4587,10 +4587,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120494059</v>
+        <v>120499409</v>
       </c>
       <c r="B38" t="n">
-        <v>79658</v>
+        <v>79131</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4599,41 +4599,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6463</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>513140</v>
+        <v>512923</v>
       </c>
       <c r="R38" t="n">
-        <v>7129002</v>
+        <v>7128543</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4689,10 +4689,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120499332</v>
+        <v>120498577</v>
       </c>
       <c r="B39" t="n">
-        <v>79659</v>
+        <v>79624</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4701,38 +4701,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>512919</v>
+        <v>512845</v>
       </c>
       <c r="R39" t="n">
-        <v>7128556</v>
+        <v>7128718</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4791,10 +4791,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120495447</v>
+        <v>120499221</v>
       </c>
       <c r="B40" t="n">
-        <v>79527</v>
+        <v>90580</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4803,25 +4803,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4831,13 +4831,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>513004</v>
+        <v>512894</v>
       </c>
       <c r="R40" t="n">
-        <v>7128839</v>
+        <v>7128619</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4893,10 +4893,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120498239</v>
+        <v>120497952</v>
       </c>
       <c r="B41" t="n">
-        <v>79623</v>
+        <v>79624</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4909,21 +4909,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4933,10 +4933,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>512784</v>
+        <v>512703</v>
       </c>
       <c r="R41" t="n">
-        <v>7128764</v>
+        <v>7128859</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4995,7 +4995,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120498176</v>
+        <v>120499316</v>
       </c>
       <c r="B42" t="n">
         <v>79624</v>
@@ -5031,14 +5031,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>512770</v>
+        <v>512920</v>
       </c>
       <c r="R42" t="n">
-        <v>7128772</v>
+        <v>7128544</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5097,10 +5097,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120499316</v>
+        <v>120498027</v>
       </c>
       <c r="B43" t="n">
-        <v>79624</v>
+        <v>79659</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5109,38 +5109,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>512920</v>
+        <v>512716</v>
       </c>
       <c r="R43" t="n">
-        <v>7128544</v>
+        <v>7128822</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5199,10 +5199,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120498596</v>
+        <v>120495447</v>
       </c>
       <c r="B44" t="n">
-        <v>79652</v>
+        <v>79527</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5215,21 +5215,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5239,13 +5239,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>512850</v>
+        <v>513004</v>
       </c>
       <c r="R44" t="n">
-        <v>7128717</v>
+        <v>7128839</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5301,10 +5301,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120498307</v>
+        <v>120498729</v>
       </c>
       <c r="B45" t="n">
-        <v>79623</v>
+        <v>79131</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5317,21 +5317,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>512792</v>
+        <v>512852</v>
       </c>
       <c r="R45" t="n">
-        <v>7128772</v>
+        <v>7128719</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5403,10 +5403,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120501523</v>
+        <v>120494800</v>
       </c>
       <c r="B46" t="n">
-        <v>79583</v>
+        <v>78187</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5415,41 +5415,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229497</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>513173</v>
+        <v>513056</v>
       </c>
       <c r="R46" t="n">
-        <v>7128614</v>
+        <v>7128924</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5505,10 +5505,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120499507</v>
+        <v>120499446</v>
       </c>
       <c r="B47" t="n">
-        <v>79623</v>
+        <v>79658</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5517,25 +5517,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5545,10 +5545,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>512911</v>
+        <v>512906</v>
       </c>
       <c r="R47" t="n">
-        <v>7128542</v>
+        <v>7128551</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5607,10 +5607,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120495236</v>
+        <v>120500096</v>
       </c>
       <c r="B48" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5623,37 +5623,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>513040</v>
+        <v>512986</v>
       </c>
       <c r="R48" t="n">
-        <v>7128866</v>
+        <v>7128475</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5683,6 +5688,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5709,10 +5719,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120495327</v>
+        <v>120500304</v>
       </c>
       <c r="B49" t="n">
-        <v>90576</v>
+        <v>79624</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5725,37 +5735,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>513039</v>
+        <v>513030</v>
       </c>
       <c r="R49" t="n">
-        <v>7128873</v>
+        <v>7128399</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5811,7 +5821,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120501050</v>
+        <v>120495236</v>
       </c>
       <c r="B50" t="n">
         <v>78542</v>
@@ -5847,17 +5857,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>513045</v>
+        <v>513040</v>
       </c>
       <c r="R50" t="n">
-        <v>7128377</v>
+        <v>7128866</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5913,10 +5923,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120498715</v>
+        <v>120499055</v>
       </c>
       <c r="B51" t="n">
-        <v>80499</v>
+        <v>79624</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5929,21 +5939,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1049</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5953,10 +5963,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>512849</v>
+        <v>512881</v>
       </c>
       <c r="R51" t="n">
-        <v>7128712</v>
+        <v>7128617</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6015,10 +6025,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120498027</v>
+        <v>120494019</v>
       </c>
       <c r="B52" t="n">
-        <v>79659</v>
+        <v>79624</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6027,25 +6037,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6055,10 +6065,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>512716</v>
+        <v>513140</v>
       </c>
       <c r="R52" t="n">
-        <v>7128822</v>
+        <v>7129010</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6117,10 +6127,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120497952</v>
+        <v>120501722</v>
       </c>
       <c r="B53" t="n">
-        <v>79624</v>
+        <v>78187</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6133,34 +6143,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>512703</v>
+        <v>513207</v>
       </c>
       <c r="R53" t="n">
-        <v>7128859</v>
+        <v>7128708</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6219,10 +6229,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120494756</v>
+        <v>120500243</v>
       </c>
       <c r="B54" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6235,39 +6245,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>513061</v>
+        <v>513023</v>
       </c>
       <c r="R54" t="n">
-        <v>7128929</v>
+        <v>7128467</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6300,11 +6305,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på granlåga</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6331,10 +6331,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120498729</v>
+        <v>120494284</v>
       </c>
       <c r="B55" t="n">
-        <v>79131</v>
+        <v>79624</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6347,21 +6347,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>512852</v>
+        <v>513104</v>
       </c>
       <c r="R55" t="n">
-        <v>7128719</v>
+        <v>7128997</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6433,10 +6433,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120495537</v>
+        <v>120498239</v>
       </c>
       <c r="B56" t="n">
-        <v>79131</v>
+        <v>79623</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6449,21 +6449,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6473,13 +6473,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>512947</v>
+        <v>512784</v>
       </c>
       <c r="R56" t="n">
-        <v>7128818</v>
+        <v>7128764</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6535,10 +6535,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120500096</v>
+        <v>120500180</v>
       </c>
       <c r="B57" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6551,42 +6551,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>512986</v>
+        <v>512964</v>
       </c>
       <c r="R57" t="n">
-        <v>7128475</v>
+        <v>7128462</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6616,11 +6611,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6647,7 +6637,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120494284</v>
+        <v>120499521</v>
       </c>
       <c r="B58" t="n">
         <v>79624</v>
@@ -6683,14 +6673,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>513104</v>
+        <v>512916</v>
       </c>
       <c r="R58" t="n">
-        <v>7128997</v>
+        <v>7128556</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6749,10 +6739,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120498585</v>
+        <v>120499482</v>
       </c>
       <c r="B59" t="n">
-        <v>79623</v>
+        <v>79659</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6761,38 +6751,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>512853</v>
+        <v>512911</v>
       </c>
       <c r="R59" t="n">
-        <v>7128713</v>
+        <v>7128542</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6851,10 +6841,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120498915</v>
+        <v>120499332</v>
       </c>
       <c r="B60" t="n">
-        <v>79623</v>
+        <v>79659</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6863,41 +6853,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>512876</v>
+        <v>512919</v>
       </c>
       <c r="R60" t="n">
-        <v>7128686</v>
+        <v>7128556</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6953,10 +6943,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120493980</v>
+        <v>120498307</v>
       </c>
       <c r="B61" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6965,25 +6955,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6993,10 +6983,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>513141</v>
+        <v>512792</v>
       </c>
       <c r="R61" t="n">
-        <v>7129006</v>
+        <v>7128772</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7055,10 +7045,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120498401</v>
+        <v>120501523</v>
       </c>
       <c r="B62" t="n">
-        <v>79624</v>
+        <v>79583</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7067,38 +7057,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>229497</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>512865</v>
+        <v>513173</v>
       </c>
       <c r="R62" t="n">
-        <v>7128745</v>
+        <v>7128614</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7157,10 +7147,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120500539</v>
+        <v>120494756</v>
       </c>
       <c r="B63" t="n">
-        <v>78187</v>
+        <v>57320</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7173,37 +7163,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>512939</v>
+        <v>513061</v>
       </c>
       <c r="R63" t="n">
-        <v>7128343</v>
+        <v>7128929</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7233,6 +7228,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på granlåga</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7259,10 +7259,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120499737</v>
+        <v>120501050</v>
       </c>
       <c r="B64" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7275,21 +7275,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7299,13 +7299,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>512923</v>
+        <v>513045</v>
       </c>
       <c r="R64" t="n">
-        <v>7128512</v>
+        <v>7128377</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120499055</v>
+        <v>120498298</v>
       </c>
       <c r="B65" t="n">
         <v>79624</v>
@@ -7401,13 +7401,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>512881</v>
+        <v>512796</v>
       </c>
       <c r="R65" t="n">
-        <v>7128617</v>
+        <v>7128766</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120501177</v>
+        <v>120498401</v>
       </c>
       <c r="B66" t="n">
         <v>79624</v>
@@ -7499,14 +7499,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>513078</v>
+        <v>512865</v>
       </c>
       <c r="R66" t="n">
-        <v>7128470</v>
+        <v>7128745</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>

--- a/artfynd/A 56894-2022 artfynd.xlsx
+++ b/artfynd/A 56894-2022 artfynd.xlsx
@@ -3465,10 +3465,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120499507</v>
+        <v>120498715</v>
       </c>
       <c r="B27" t="n">
-        <v>79623</v>
+        <v>80499</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3481,34 +3481,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>512911</v>
+        <v>512849</v>
       </c>
       <c r="R27" t="n">
-        <v>7128542</v>
+        <v>7128712</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3567,10 +3567,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120498715</v>
+        <v>120499507</v>
       </c>
       <c r="B28" t="n">
-        <v>80499</v>
+        <v>79623</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3583,34 +3583,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>512849</v>
+        <v>512911</v>
       </c>
       <c r="R28" t="n">
-        <v>7128712</v>
+        <v>7128542</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -5719,10 +5719,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120500304</v>
+        <v>120495236</v>
       </c>
       <c r="B49" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5735,37 +5735,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>513030</v>
+        <v>513040</v>
       </c>
       <c r="R49" t="n">
-        <v>7128399</v>
+        <v>7128866</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5821,10 +5821,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120495236</v>
+        <v>120500304</v>
       </c>
       <c r="B50" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5837,37 +5837,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>513040</v>
+        <v>513030</v>
       </c>
       <c r="R50" t="n">
-        <v>7128866</v>
+        <v>7128399</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7045,10 +7045,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120501523</v>
+        <v>120494756</v>
       </c>
       <c r="B62" t="n">
-        <v>79583</v>
+        <v>57320</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7057,38 +7057,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>513173</v>
+        <v>513061</v>
       </c>
       <c r="R62" t="n">
-        <v>7128614</v>
+        <v>7128929</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7121,6 +7126,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på granlåga</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7147,10 +7157,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120494756</v>
+        <v>120501523</v>
       </c>
       <c r="B63" t="n">
-        <v>57320</v>
+        <v>79583</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7159,43 +7169,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+          <t>Bäckmyrtjärnen, Bäckmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>513061</v>
+        <v>513173</v>
       </c>
       <c r="R63" t="n">
-        <v>7128929</v>
+        <v>7128614</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7228,11 +7233,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på granlåga</t>
         </is>
       </c>
       <c r="AD63" t="b">
